--- a/output/pdf_financials_xlsx/OWLI.xlsx
+++ b/output/pdf_financials_xlsx/OWLI.xlsx
@@ -2039,10 +2039,10 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.445362</v>
+        <v>1.83894</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.452262</v>
+        <v>1.87153</v>
       </c>
     </row>
     <row r="93">
@@ -3422,7 +3422,11 @@
           <t>Share-based payments and warrants reserve 9</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/OWLI.xlsx
+++ b/output/pdf_financials_xlsx/OWLI.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.862714</v>
+        <v>1.564683</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.822269</v>
+        <v>1.136421</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.675325</v>
+        <v>0.857031</v>
       </c>
     </row>
     <row r="11">
@@ -990,7 +990,7 @@
         <v>0</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>4.3e-05</v>
       </c>
     </row>
     <row r="35">
@@ -1026,7 +1026,7 @@
         <v>0</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>4.3e-05</v>
       </c>
     </row>
     <row r="37">
@@ -1242,7 +1242,7 @@
         <v>0.051321</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.022101</v>
+        <v>0.022058</v>
       </c>
     </row>
     <row r="49">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -4907,17 +4907,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>-1.564683</v>
+        <v>1.564683</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>-1.136421</v>
+        <v>1.136421</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>-0.857031</v>
+        <v>0.857031</v>
       </c>
     </row>
     <row r="71">

--- a/output/pdf_financials_xlsx/OWLI.xlsx
+++ b/output/pdf_financials_xlsx/OWLI.xlsx
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>-0</v>
+        <v>0.041772</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>-0</v>
+        <v>0.6178439999999999</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>-0</v>
@@ -867,10 +867,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.621001</v>
+        <v>-1.662773</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.741268</v>
+        <v>-2.359112</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-1.195886</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.621001</v>
+        <v>-1.662773</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.741268</v>
+        <v>-2.359112</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-1.195886</v>
@@ -5839,7 +5839,11 @@
           <t>Net financing cost</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E100" s="5" t="n">
         <v>-0.041772</v>
       </c>

--- a/output/pdf_financials_xlsx/OWLI.xlsx
+++ b/output/pdf_financials_xlsx/OWLI.xlsx
@@ -981,10 +981,8 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>0.007446</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0</v>
@@ -999,10 +997,8 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C35" s="3" t="n">
         <v>0</v>
@@ -1017,10 +1013,8 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0.007446</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0</v>
@@ -1035,10 +1029,8 @@
           <t xml:space="preserve">    Accounts Receivable</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B37" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C37" s="3" t="n">
         <v>0</v>
@@ -1053,10 +1045,8 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C38" s="3" t="n">
         <v>0</v>
@@ -1071,10 +1061,8 @@
           <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C39" s="3" t="n">
         <v>0</v>
@@ -1089,10 +1077,8 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>0</v>
@@ -1107,10 +1093,8 @@
           <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C41" s="3" t="n">
         <v>0</v>
@@ -1125,10 +1109,8 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C42" s="3" t="n">
         <v>0</v>
@@ -1143,10 +1125,8 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C43" s="3" t="n">
         <v>0</v>
@@ -1161,10 +1141,8 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C44" s="3" t="n">
         <v>0</v>
@@ -1179,10 +1157,8 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C45" s="3" t="n">
         <v>0</v>
@@ -1197,10 +1173,8 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C46" s="3" t="n">
         <v>0</v>
@@ -1215,10 +1189,8 @@
           <t xml:space="preserve">  Total Inventories</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C47" s="3" t="n">
         <v>0</v>
@@ -1233,10 +1205,8 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>0.043644</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.051321</v>
@@ -1251,10 +1221,8 @@
           <t xml:space="preserve">  Total Current Assets</t>
         </is>
       </c>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B49" s="3" t="n">
+        <v>0.05109</v>
       </c>
       <c r="C49" s="3" t="n">
         <v>0.051321</v>
@@ -1269,10 +1237,8 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C50" s="3" t="n">
         <v>0</v>
@@ -1287,10 +1253,8 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C51" s="3" t="n">
         <v>0</v>
@@ -1305,10 +1269,8 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C52" s="3" t="n">
         <v>0</v>
@@ -1323,10 +1285,8 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C53" s="3" t="n">
         <v>0</v>
@@ -1341,10 +1301,8 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C54" s="3" t="n">
         <v>0</v>
@@ -1381,10 +1339,8 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C56" s="3" t="n">
         <v>0</v>
@@ -1399,10 +1355,8 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C57" s="3" t="n">
         <v>0</v>
@@ -1417,10 +1371,8 @@
           <t xml:space="preserve">  Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C58" s="3" t="n">
         <v>0</v>
@@ -1435,10 +1387,8 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C59" s="3" t="n">
         <v>0.015</v>
@@ -1453,10 +1403,8 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C60" s="3" t="n">
         <v>0</v>
@@ -1471,10 +1419,8 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C61" s="3" t="n">
         <v>0</v>
@@ -1489,10 +1435,8 @@
           <t xml:space="preserve">  Total Long-Term Assets</t>
         </is>
       </c>
-      <c r="B62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B62" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C62" s="3" t="n">
         <v>0.015</v>
@@ -1507,10 +1451,8 @@
           <t>Total Assets</t>
         </is>
       </c>
-      <c r="B63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B63" s="3" t="n">
+        <v>0.05109</v>
       </c>
       <c r="C63" s="3" t="n">
         <v>0.066321</v>
@@ -1525,10 +1467,8 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
         <v>0</v>
@@ -1543,10 +1483,8 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C65" s="3" t="n">
         <v>0</v>
@@ -1561,10 +1499,8 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0.311976</v>
       </c>
       <c r="C66" s="3" t="n">
         <v>0.5667450000000001</v>
@@ -1579,10 +1515,8 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>1.151247</v>
       </c>
       <c r="C67" s="3" t="n">
         <v>1.608514</v>
@@ -1597,10 +1531,8 @@
           <t xml:space="preserve">  Accounts Payable &amp; Accrued Expense</t>
         </is>
       </c>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B68" s="3" t="n">
+        <v>1.151247</v>
       </c>
       <c r="C68" s="3" t="n">
         <v>1.608514</v>
@@ -1615,10 +1547,8 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C69" s="3" t="n">
         <v>0</v>
@@ -1633,10 +1563,8 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C70" s="3" t="n">
         <v>0</v>
@@ -1651,10 +1579,8 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C71" s="3" t="n">
         <v>0</v>
@@ -1669,10 +1595,8 @@
           <t xml:space="preserve">    Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C72" s="3" t="n">
         <v>0</v>
@@ -1687,10 +1611,8 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C73" s="3" t="n">
         <v>0</v>
@@ -1705,10 +1627,8 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C74" s="3" t="n">
         <v>0</v>
@@ -1723,10 +1643,8 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>0.393738</v>
       </c>
       <c r="C75" s="3" t="n">
         <v>0.569782</v>
@@ -1741,10 +1659,8 @@
           <t xml:space="preserve">  Total Current Liabilities</t>
         </is>
       </c>
-      <c r="B76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B76" s="3" t="n">
+        <v>1.544985</v>
       </c>
       <c r="C76" s="3" t="n">
         <v>2.178296</v>
@@ -1759,10 +1675,8 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C77" s="3" t="n">
         <v>0</v>
@@ -1777,10 +1691,8 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C78" s="3" t="n">
         <v>0</v>
@@ -1795,10 +1707,8 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C79" s="3" t="n">
         <v>0</v>
@@ -1835,10 +1745,8 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C81" s="3" t="n">
         <v>0</v>
@@ -1853,10 +1761,8 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C82" s="3" t="n">
         <v>0</v>
@@ -1871,10 +1777,8 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C83" s="3" t="n">
         <v>0</v>
@@ -1889,10 +1793,8 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C84" s="3" t="n">
         <v>0</v>
@@ -1907,10 +1809,8 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>0.06</v>
       </c>
       <c r="C85" s="3" t="n">
         <v>0.06</v>
@@ -1925,10 +1825,8 @@
           <t xml:space="preserve">  Total Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B86" s="3" t="n">
+        <v>0.06</v>
       </c>
       <c r="C86" s="3" t="n">
         <v>0.06</v>
@@ -1943,10 +1841,8 @@
           <t>Total Liabilities</t>
         </is>
       </c>
-      <c r="B87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B87" s="3" t="n">
+        <v>1.604985</v>
       </c>
       <c r="C87" s="3" t="n">
         <v>2.238296</v>
@@ -1961,10 +1857,8 @@
           <t xml:space="preserve">  Common Stock</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>23.694382</v>
       </c>
       <c r="C88" s="3" t="n">
         <v>24.081365</v>
@@ -1979,10 +1873,8 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C89" s="3" t="n">
         <v>0</v>
@@ -1997,10 +1889,8 @@
           <t xml:space="preserve">  Retained Earnings</t>
         </is>
       </c>
-      <c r="B90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B90" s="3" t="n">
+        <v>-26.509662</v>
       </c>
       <c r="C90" s="3" t="n">
         <v>-28.09228</v>
@@ -2015,10 +1905,8 @@
           <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C91" s="3" t="n">
         <v>0</v>
@@ -2033,10 +1921,8 @@
           <t xml:space="preserve">  Additional Paid-In Capital</t>
         </is>
       </c>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="3" t="n">
+        <v>1.261385</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>1.83894</v>
@@ -2051,10 +1937,8 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C93" s="3" t="n">
         <v>0</v>
@@ -2069,10 +1953,8 @@
           <t xml:space="preserve">  Total Stockholders Equity</t>
         </is>
       </c>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="3" t="n">
+        <v>-1.553895</v>
       </c>
       <c r="C94" s="3" t="n">
         <v>-2.171975</v>
@@ -2087,10 +1969,8 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C95" s="3" t="n">
         <v>0</v>
@@ -2105,10 +1985,8 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B96" s="3" t="n">
+        <v>-1.553895</v>
       </c>
       <c r="C96" s="3" t="n">
         <v>-2.171975</v>
@@ -2123,10 +2001,8 @@
           <t>Equity-to-Asset</t>
         </is>
       </c>
-      <c r="B97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B97" s="3" t="n">
+        <v>-30.41485613623018</v>
       </c>
       <c r="C97" s="3" t="n">
         <v>-32.74943079869121</v>
@@ -2755,7 +2631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G125"/>
+  <dimension ref="A1:G131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2818,10 +2694,8 @@
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E2" s="5" t="n">
+        <v>0.002024</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>0.002025</v>
@@ -2938,10 +2812,8 @@
           <t>CashAndCashEquivalents</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E6" s="5" t="n">
+        <v>0.007446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2969,10 +2841,8 @@
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E7" s="5" t="n">
+        <v>0.038871</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0.046012</v>
@@ -3002,10 +2872,8 @@
           <t>PrepaidAssets</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E8" s="5" t="n">
+        <v>0.004773</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>0.005309</v>
@@ -3037,10 +2905,8 @@
           <t>CurrentAssets</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E9" s="5" t="n">
+        <v>0.05109</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>0.051321</v>
@@ -3103,10 +2969,8 @@
           <t>TotalAssets</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E11" s="5" t="n">
+        <v>0.05109</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>0.066321</v>
@@ -3169,10 +3033,8 @@
           <t>OtherPayable</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E13" s="5" t="n">
+        <v>0.311976</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>0.5667450000000001</v>
@@ -3198,10 +3060,8 @@
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E14" s="5" t="n">
+        <v>0.021508</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>0.0015</v>
@@ -3328,10 +3188,8 @@
           <t>TotalLiabilities</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E18" s="5" t="n">
+        <v>1.604985</v>
       </c>
       <c r="F18" s="5" t="n">
         <v>2.238296</v>
@@ -3361,10 +3219,8 @@
           <t>CapitalStock</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E19" s="5" t="n">
+        <v>23.694382</v>
       </c>
       <c r="F19" s="5" t="n">
         <v>24.081365</v>
@@ -3394,10 +3250,8 @@
           <t>AdditionalPaidInCapital</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E20" s="5" t="n">
+        <v>0.428088</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>0.445362</v>
@@ -3427,10 +3281,8 @@
           <t>AdditionalPaidInCapital</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E21" s="5" t="n">
+        <v>0.833297</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>1.393578</v>
@@ -3460,10 +3312,8 @@
           <t>RetainedEarnings</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E22" s="5" t="n">
+        <v>-26.509662</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>-28.09228</v>
@@ -3493,10 +3343,8 @@
           <t>StockholdersEquity</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E23" s="5" t="n">
+        <v>-1.553895</v>
       </c>
       <c r="F23" s="5" t="n">
         <v>-2.171975</v>
@@ -3526,10 +3374,8 @@
           <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E24" s="5" t="n">
+        <v>0.05109</v>
       </c>
       <c r="F24" s="5" t="n">
         <v>0.066321</v>
@@ -3570,172 +3416,180 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Vancouver, Canada</t>
+        </is>
+      </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>December 31, 2025 December</t>
+          <t>July</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E26" s="5" t="n">
+        <v>0.002025</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>3e-06</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>OPERATING ACTIVITIES</t>
+          <t>Vancouver, Canada</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Net loss $</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+          <t>As of December 31, 2024 and December</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" s="5" t="n">
-        <v>-1.621001</v>
+        <v>0.002023</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>-1.741268</v>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>-1.195886</v>
+        <v>3.1e-05</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Non-cash items</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Share-based payments</t>
+          <t>Accounts payables and accrued liabilities 6</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
+          <t>CurrentAccruedExpenses</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0.287089</v>
+        <v>1.151247</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.063911</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>0.00425</v>
+        <v>1.608514</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Non-cash items</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Net financing cost</t>
+          <t>Share subscriptions payable 8(ii)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" s="5" t="n">
-        <v>0.041772</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>0.6178439999999999</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>0.340578</v>
+        <v>0.060254</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Non-cash items</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Gain from debt settlement</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>-0.00287</v>
+          <t>Current liabilities total</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CurrentLiabilities</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>1.544985</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>2.178296</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Non-cash items</t>
+          <t>Events after reporting period</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Gain from debt write-off</t>
+          <t>Approved on behalf of the Board of Directors on July</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E31" s="5" t="n">
+        <v>0.002025</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>-0.016252</v>
+        <v>3e-06</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -3749,25 +3603,23 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Changes in non-cash working capital items</t>
-        </is>
-      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Receivables and advances</t>
+          <t>December 31, 2025 December</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" s="5" t="n">
-        <v>-0.016152</v>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>-0.007141</v>
+        <v>0.002024</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.023954</v>
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="33">
@@ -3778,27 +3630,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Prepaid expenses and deposits</t>
+          <t>Net loss $</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0.005655</v>
+        <v>-1.621001</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>-0.000536</v>
+        <v>-1.741268</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.005309</v>
+        <v>-1.195886</v>
       </c>
     </row>
     <row r="34">
@@ -3809,27 +3661,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
+          <t>Share-based payments</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0.530537</v>
+        <v>0.287089</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.443986</v>
+        <v>0.063911</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.426966</v>
+        <v>0.00425</v>
       </c>
     </row>
     <row r="35">
@@ -3840,23 +3692,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Due to related parties</t>
+          <t>Net financing cost</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" s="5" t="n">
-        <v>0.26629</v>
+        <v>0.041772</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>0.254769</v>
+        <v>0.6178439999999999</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.276191</v>
+        <v>0.340578</v>
       </c>
     </row>
     <row r="36">
@@ -3867,27 +3719,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities $</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>-0.48581</v>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>-0.384687</v>
+          <t>Gain from debt settlement</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.121508</v>
+        <v>-0.00287</v>
       </c>
     </row>
     <row r="37">
@@ -3898,20 +3750,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Repayment of loans and borrowings $</t>
+          <t>Gain from debt write-off</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" s="5" t="n">
-        <v>-0.0142</v>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>-0.014516</v>
+        <v>-0.016252</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -3927,25 +3781,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Proceeds from loans and borrowings</t>
+          <t>Receivables and advances</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E38" s="5" t="n">
+        <v>-0.016152</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.007141</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.1072</v>
+        <v>0.023954</v>
       </c>
     </row>
     <row r="39">
@@ -3956,29 +3808,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of shares</t>
+          <t>Prepaid expenses and deposits</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CommonStockIssuance</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>0.005655</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>0.382757</v>
+        <v>-0.000536</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.014351</v>
+        <v>0.005309</v>
       </c>
     </row>
     <row r="40">
@@ -3989,29 +3839,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities $</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>0.530537</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>0.377241</v>
+        <v>0.443986</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.121551</v>
+        <v>0.426966</v>
       </c>
     </row>
     <row r="41">
@@ -4022,25 +3870,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Net increase (decrease) in cash in the year $</t>
+          <t>Due to related parties</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E41" s="5" t="n">
+        <v>0.26629</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>-0.007446</v>
+        <v>0.254769</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>4.3e-05</v>
+        <v>0.276191</v>
       </c>
     </row>
     <row r="42">
@@ -4051,27 +3897,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cash – opening balance $</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net cash used in operating activities $</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>-0.48581</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.007446</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.384687</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>-0.121508</v>
       </c>
     </row>
     <row r="43">
@@ -4082,27 +3928,25 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cash – ending balance $</t>
+          <t>Repayment of loans and borrowings $</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>4.3e-05</v>
+      <c r="E43" s="5" t="n">
+        <v>-0.0142</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>-0.014516</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -4113,12 +3957,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>December 31, 2025 December</t>
+          <t>Proceeds from loans and borrowings</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -4128,10 +3972,10 @@
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.002024</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.1072</v>
       </c>
     </row>
     <row r="45">
@@ -4142,25 +3986,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Share purchase warrants issued in lieu of financing cost $</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>Proceeds from issuance of shares</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>0.00624</v>
+        <v>0.382757</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.07504</v>
+        <v>0.014351</v>
       </c>
     </row>
     <row r="46">
@@ -4171,27 +4019,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Shares issued to acquire intangible assets $</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>Net cash provided by financing activities $</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.377241</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0.121551</v>
       </c>
     </row>
     <row r="47">
@@ -4202,12 +4052,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Shares issued to settle loans and borrowings $</t>
+          <t>Net increase (decrease) in cash in the year $</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -4217,12 +4067,10 @@
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.007446</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>4.3e-05</v>
       </c>
     </row>
     <row r="48">
@@ -4233,31 +4081,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Shares issued to settle accounts payable $</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
+          <t>Cash – opening balance $</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="n">
-        <v>0.014351</v>
+      <c r="F48" s="5" t="n">
+        <v>0.007446</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -4268,12 +4112,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Warrant modification $</t>
+          <t>Cash – ending balance $</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -4282,11 +4126,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F49" s="5" t="n">
-        <v>0.571026</v>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.2333</v>
+        <v>4.3e-05</v>
       </c>
     </row>
     <row r="50">
@@ -4302,7 +4148,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Expiration of options $</t>
+          <t>December 31, 2025 December</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -4312,10 +4158,10 @@
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0.15865</v>
+        <v>0.002024</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.28</v>
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="51">
@@ -4331,7 +4177,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Expiration of warrants $</t>
+          <t>Share purchase warrants issued in lieu of financing cost $</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -4341,10 +4187,10 @@
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>0.017274</v>
+        <v>0.00624</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.07504</v>
       </c>
     </row>
     <row r="52">
@@ -4355,12 +4201,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>subsidiary.</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>These consolidated financial statements were approved and authorized for issuance by the Board of Directors on April</t>
+          <t>Shares issued to acquire intangible assets $</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -4370,10 +4216,12 @@
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.002026</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>2.9e-05</v>
+        <v>0.015</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -4382,18 +4230,24 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Supplemental cash flow information</t>
+        </is>
+      </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>For the year ended: December 31, 2024 December</t>
+          <t>Shares issued to settle loans and borrowings $</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" s="5" t="n">
-        <v>0.002023</v>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.024</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -4409,27 +4263,31 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Non-cash items</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Other expenses</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" s="5" t="n">
-        <v>0.02</v>
+          <t>Shares issued to settle accounts payable $</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G54" s="5" t="n">
+        <v>0.014351</v>
       </c>
     </row>
     <row r="55">
@@ -4440,25 +4298,25 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Proceeds from loans, net of transaction costs</t>
+          <t>Warrant modification $</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" s="5" t="n">
-        <v>0.015</v>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.571026</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.2333</v>
       </c>
     </row>
     <row r="56">
@@ -4469,27 +4327,25 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Advance for private placement</t>
+          <t>Expiration of options $</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" s="5" t="n">
-        <v>0.060254</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>0.15865</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.28</v>
       </c>
     </row>
     <row r="57">
@@ -4500,29 +4356,25 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities $</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="n">
-        <v>0.260854</v>
+          <t>Expiration of warrants $</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>0.377241</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.017274</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.0069</v>
       </c>
     </row>
     <row r="58">
@@ -4533,25 +4385,25 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>subsidiary.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Net decrease in cash in the year $</t>
+          <t>These consolidated financial statements were approved and authorized for issuance by the Board of Directors on April</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" s="5" t="n">
-        <v>-0.224956</v>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>-0.007446</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002026</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>2.9e-05</v>
       </c>
     </row>
     <row r="59">
@@ -4560,26 +4412,18 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>FINANCING ACTIVITIES</t>
-        </is>
-      </c>
+      <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cash – beginning of the year $</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>For the year ended: December 31, 2024 December</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" s="5" t="n">
-        <v>0.232402</v>
+        <v>0.002023</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>0.007446</v>
+        <v>3.1e-05</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -4595,21 +4439,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cash – ending of the year $</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Other expenses</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" s="5" t="n">
-        <v>0.007446</v>
+        <v>0.02</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4630,20 +4470,20 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>For the year ended: Notes December 31, 2024 December</t>
+          <t>Proceeds from loans, net of transaction costs</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" s="5" t="n">
-        <v>0.002023</v>
+        <v>0.015</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -4659,20 +4499,26 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Share purchase warrants issued in lieu of financing cost 7 $</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
+          <t>Advance for private placement</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E62" s="5" t="n">
-        <v>0.0069</v>
-      </c>
-      <c r="F62" s="5" t="n">
-        <v>0.00624</v>
+        <v>0.060254</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -4688,22 +4534,24 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Shares issued to acquire intangible assets</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net cash provided by financing activities $</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>0.260854</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>0.015</v>
+        <v>0.377241</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -4719,22 +4567,20 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Shares issued to settle loans and borrowings</t>
+          <t>Net decrease in cash in the year $</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E64" s="5" t="n">
+        <v>-0.224956</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>0.024</v>
+        <v>-0.007446</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -4750,20 +4596,24 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>subsidiary.</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>These consolidated financial statements were approved and authorized for issuance by the Board of Directors on July</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>Cash – beginning of the year $</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E65" s="5" t="n">
-        <v>0.002025</v>
+        <v>0.232402</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>3e-06</v>
+        <v>0.007446</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -4774,106 +4624,110 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Notes 2025 December</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F66" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="G66" s="5" t="n">
-        <v>3.1e-05</v>
+          <t>Cash – ending of the year $</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>0.007446</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>General and administration 10 $</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>For the year ended: Notes December 31, 2024 December</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" s="5" t="n">
+        <v>0.002023</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>0.250241</v>
-      </c>
-      <c r="G67" s="5" t="n">
-        <v>0.177456</v>
+        <v>3.1e-05</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Professional and consulting fees 10</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Share purchase warrants issued in lieu of financing cost 7 $</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" s="5" t="n">
-        <v>0.862714</v>
+        <v>0.0069</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>0.822269</v>
-      </c>
-      <c r="G68" s="5" t="n">
-        <v>0.675325</v>
+        <v>0.00624</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Share-based payments 9,10</t>
+          <t>Shares issued to acquire intangible assets</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -4883,72 +4737,72 @@
         </is>
       </c>
       <c r="F69" s="5" t="n">
-        <v>0.063911</v>
-      </c>
-      <c r="G69" s="5" t="n">
-        <v>0.00425</v>
+        <v>0.015</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Total expenses $</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="n">
-        <v>1.564683</v>
+          <t>Shares issued to settle loans and borrowings</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F70" s="5" t="n">
-        <v>1.136421</v>
-      </c>
-      <c r="G70" s="5" t="n">
-        <v>0.857031</v>
+        <v>0.024</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>subsidiary.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Operating loss $</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>These consolidated financial statements were approved and authorized for issuance by the Board of Directors on July</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" s="5" t="n">
-        <v>-1.564683</v>
+        <v>0.002025</v>
       </c>
       <c r="F71" s="5" t="n">
-        <v>-1.136421</v>
-      </c>
-      <c r="G71" s="5" t="n">
-        <v>-0.857031</v>
+        <v>3e-06</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -4957,14 +4811,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Other expenses</t>
-        </is>
-      </c>
+      <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Net financing cost 8(b)(iv)</t>
+          <t>Notes 2025 December</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -4974,10 +4824,10 @@
         </is>
       </c>
       <c r="F72" s="5" t="n">
-        <v>-0.6178439999999999</v>
+        <v>0.002024</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>-0.340578</v>
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="73">
@@ -4988,17 +4838,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
+          <t>General and administration 10 $</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -5007,10 +4857,10 @@
         </is>
       </c>
       <c r="F73" s="5" t="n">
-        <v>-0.003255</v>
+        <v>0.250241</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>-0.001147</v>
+        <v>0.177456</v>
       </c>
     </row>
     <row r="74">
@@ -5021,27 +4871,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Gain from debt settlement 8(a)(iv)</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Professional and consulting fees 10</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>0.862714</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>0.822269</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.00287</v>
+        <v>0.675325</v>
       </c>
     </row>
     <row r="75">
@@ -5052,12 +4902,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Gain from debt write-off</t>
+          <t>Share-based payments 9,10</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -5067,12 +4917,10 @@
         </is>
       </c>
       <c r="F75" s="5" t="n">
-        <v>0.016252</v>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.063911</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>0.00425</v>
       </c>
     </row>
     <row r="76">
@@ -5083,29 +4931,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss $</t>
+          <t>Total expenses $</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>1.564683</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>-1.741268</v>
+        <v>1.136421</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>-1.195886</v>
+        <v>0.857031</v>
       </c>
     </row>
     <row r="77">
@@ -5116,29 +4962,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share $</t>
+          <t>Operating loss $</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>-1.564683</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>-1e-08</v>
+        <v>-1.136421</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>-1e-08</v>
+        <v>-0.857031</v>
       </c>
     </row>
     <row r="78">
@@ -5149,12 +4993,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding –</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding – basic and diluted</t>
+          <t>Net financing cost 8(b)(iv)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -5164,10 +5008,10 @@
         </is>
       </c>
       <c r="F78" s="5" t="n">
-        <v>201.250233</v>
+        <v>-0.6178439999999999</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>213.369233</v>
+        <v>-0.340578</v>
       </c>
     </row>
     <row r="79">
@@ -5178,25 +5022,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Notes              capital             surplus           reserve                 deficit               deficit</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Balance as of December 31, 2023 $ 23,694,382 $ 428,088 $ 833,297 $</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F79" s="5" t="n">
-        <v>-1.553895</v>
+        <v>-0.003255</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>-26.509662</v>
+        <v>-0.001147</v>
       </c>
     </row>
     <row r="80">
@@ -5207,12 +5055,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Notes              capital             surplus           reserve                 deficit               deficit</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Shares issued in private placement 8(a) 347,983 – 95,028</t>
+          <t>Gain from debt settlement 8(a)(iv)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -5221,13 +5069,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F80" s="5" t="n">
-        <v>0.443011</v>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>0.00287</v>
       </c>
     </row>
     <row r="81">
@@ -5238,12 +5086,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Notes              capital             surplus           reserve                 deficit               deficit</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Shares issued to acquire intangible assets 8(a) 15,000 – –</t>
+          <t>Gain from debt write-off</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -5253,7 +5101,7 @@
         </is>
       </c>
       <c r="F81" s="5" t="n">
-        <v>0.015</v>
+        <v>0.016252</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -5269,27 +5117,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Notes              capital             surplus           reserve                 deficit               deficit</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Shares issued to settle loans and borrowings 8(a) 24,000 – –</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>Net loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F82" s="5" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.741268</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>-1.195886</v>
       </c>
     </row>
     <row r="83">
@@ -5300,27 +5150,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Notes              capital             surplus           reserve                 deficit               deficit</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Share-based payments 9(a) – – 63,911</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
+          <t>Basic and diluted loss per common share $</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F83" s="5" t="n">
-        <v>0.063911</v>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1e-08</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>-1e-08</v>
       </c>
     </row>
     <row r="84">
@@ -5331,12 +5183,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Notes              capital             surplus           reserve                 deficit               deficit</t>
+          <t>Weighted average number of common shares outstanding –</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Warrant modification 8(b) – – 571,026</t>
+          <t>Weighted average number of common shares outstanding – basic and diluted</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -5346,12 +5198,10 @@
         </is>
       </c>
       <c r="F84" s="5" t="n">
-        <v>0.571026</v>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>201.250233</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>213.369233</v>
       </c>
     </row>
     <row r="85">
@@ -5367,7 +5217,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Warrants issued on loan payable 8(b(i)) – – 6,240</t>
+          <t>Balance as of December 31, 2023 $ 23,694,382 $ 428,088 $ 833,297 $</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -5377,12 +5227,10 @@
         </is>
       </c>
       <c r="F85" s="5" t="n">
-        <v>0.00624</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.553895</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>-26.509662</v>
       </c>
     </row>
     <row r="86">
@@ -5398,7 +5246,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Transfer of warrants expired 8(b) – 17,274 (17,274)</t>
+          <t>Shares issued in private placement 8(a) 347,983 – 95,028</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -5407,10 +5255,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F86" s="5" t="n">
+        <v>0.443011</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -5431,7 +5277,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Transfer of share-based payments expired 9(a(iv)) – – (158,650)</t>
+          <t>Shares issued to acquire intangible assets 8(a) 15,000 – –</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -5440,13 +5286,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G87" s="5" t="n">
-        <v>0.15865</v>
+      <c r="F87" s="5" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -5462,24 +5308,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Net loss for the period – – –</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Shares issued to settle loans and borrowings 8(a) 24,000 – –</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F88" s="5" t="n">
-        <v>-1.741268</v>
-      </c>
-      <c r="G88" s="5" t="n">
-        <v>-1.741268</v>
+        <v>0.024</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -5495,7 +5339,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Balance as of December 31, 2024 $ 24,081,365 $ 445,362 $ 1,393,578 $</t>
+          <t>Share-based payments 9(a) – – 63,911</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -5505,10 +5349,12 @@
         </is>
       </c>
       <c r="F89" s="5" t="n">
-        <v>-2.171975</v>
-      </c>
-      <c r="G89" s="5" t="n">
-        <v>-28.09228</v>
+        <v>0.063911</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="90">
@@ -5524,7 +5370,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Shares issued to settle accounts payable 8(a)(iv) 14,351 – –</t>
+          <t>Warrant modification 8(b) – – 571,026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -5534,7 +5380,7 @@
         </is>
       </c>
       <c r="F90" s="5" t="n">
-        <v>0.014351</v>
+        <v>0.571026</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -5555,7 +5401,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Share based payments 9(a) – – 4,250</t>
+          <t>Warrants issued on loan payable 8(b(i)) – – 6,240</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -5565,7 +5411,7 @@
         </is>
       </c>
       <c r="F91" s="5" t="n">
-        <v>0.00425</v>
+        <v>0.00624</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -5586,7 +5432,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Warrants issued on loans and borrowings 8(b)(iii) – – 75,040</t>
+          <t>Transfer of warrants expired 8(b) – 17,274 (17,274)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -5595,8 +5441,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F92" s="5" t="n">
-        <v>0.07504</v>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -5617,7 +5465,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Transfer of warrants expired 8 – 6,900 (6,900)</t>
+          <t>Transfer of share-based payments expired 9(a(iv)) – – (158,650)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -5631,10 +5479,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G93" s="5" t="n">
+        <v>0.15865</v>
       </c>
     </row>
     <row r="94">
@@ -5650,22 +5496,24 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Transfer of options expired 9(a)(iv) – – (280,000)</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
+          <t>Net loss for the period – – –</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F94" s="5" t="n">
+        <v>-1.741268</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.28</v>
+        <v>-1.741268</v>
       </c>
     </row>
     <row r="95">
@@ -5681,7 +5529,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Warrant modification 8(b)(iv) – – 233,300</t>
+          <t>Balance as of December 31, 2024 $ 24,081,365 $ 445,362 $ 1,393,578 $</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -5691,12 +5539,10 @@
         </is>
       </c>
       <c r="F95" s="5" t="n">
-        <v>0.2333</v>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.171975</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>-28.09228</v>
       </c>
     </row>
     <row r="96">
@@ -5712,7 +5558,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Balance as of December 31, 2025 $ 24,095,716 $ 452,262 $ 1,419,268 $</t>
+          <t>Shares issued to settle accounts payable 8(a)(iv) 14,351 – –</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -5722,10 +5568,12 @@
         </is>
       </c>
       <c r="F96" s="5" t="n">
-        <v>-3.056563</v>
-      </c>
-      <c r="G96" s="5" t="n">
-        <v>-29.023809</v>
+        <v>0.014351</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="97">
@@ -5736,12 +5584,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Notes              capital             surplus           reserve                 deficit               deficit</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Exploration and evaluation $</t>
+          <t>Share based payments 9(a) – – 4,250</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -5750,10 +5598,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F97" s="5" t="n">
+        <v>0.00425</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -5769,24 +5615,22 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Notes              capital             surplus           reserve                 deficit               deficit</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>General and administration 10</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E98" s="5" t="n">
-        <v>0.41488</v>
+          <t>Warrants issued on loans and borrowings 8(b)(iii) – – 75,040</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F98" s="5" t="n">
-        <v>0.250241</v>
+        <v>0.07504</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -5802,20 +5646,24 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Notes              capital             surplus           reserve                 deficit               deficit</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Share-based payments 8,10</t>
+          <t>Transfer of warrants expired 8 – 6,900 (6,900)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
-      <c r="E99" s="5" t="n">
-        <v>0.287089</v>
-      </c>
-      <c r="F99" s="5" t="n">
-        <v>0.063911</v>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -5831,29 +5679,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Notes              capital             surplus           reserve                 deficit               deficit</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Net financing cost</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>InterestExpenseNonOperating</t>
-        </is>
-      </c>
-      <c r="E100" s="5" t="n">
-        <v>-0.041772</v>
-      </c>
-      <c r="F100" s="5" t="n">
-        <v>-0.6178439999999999</v>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Transfer of options expired 9(a)(iv) – – (280,000)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>0.28</v>
       </c>
     </row>
     <row r="101">
@@ -5864,24 +5710,22 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Notes              capital             surplus           reserve                 deficit               deficit</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Foreign exchange loss/gain</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E101" s="5" t="n">
-        <v>-0.001514</v>
+          <t>Warrant modification 8(b)(iv) – – 233,300</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F101" s="5" t="n">
-        <v>-0.003255</v>
+        <v>0.2333</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -5897,12 +5741,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Notes              capital             surplus           reserve                 deficit               deficit</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Gain from debt extinguishment</t>
+          <t>Balance as of December 31, 2025 $ 24,095,716 $ 452,262 $ 1,419,268 $</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -5911,15 +5755,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F102" s="5" t="n">
+        <v>-3.056563</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>-29.023809</v>
       </c>
     </row>
     <row r="103">
@@ -5930,20 +5770,24 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Gain from debt write-off</t>
+          <t>Exploration and evaluation $</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
-      <c r="E103" s="5" t="n">
-        <v>0.006968</v>
-      </c>
-      <c r="F103" s="5" t="n">
-        <v>0.016252</v>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -5959,26 +5803,24 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>General and administration 10</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.41488</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>0.250241</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -5994,24 +5836,20 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share-based payments 8,10</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" s="5" t="n">
-        <v>-1.621001</v>
+        <v>0.287089</v>
       </c>
       <c r="F105" s="5" t="n">
-        <v>-1.741268</v>
+        <v>0.063911</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -6032,19 +5870,19 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share $</t>
+          <t>Net financing cost</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>InterestExpenseNonOperating</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>-1e-08</v>
+        <v>-0.041772</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>-1e-08</v>
+        <v>-0.6178439999999999</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -6065,15 +5903,19 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding – basic and diluted</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
+          <t>Foreign exchange loss/gain</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E107" s="5" t="n">
-        <v>194.866032</v>
+        <v>-0.001514</v>
       </c>
       <c r="F107" s="5" t="n">
-        <v>201.250233</v>
+        <v>-0.003255</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -6089,20 +5931,24 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Notes          Share capital                surplus               reserve                   Deficit                 equity</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Balance as at December 31, 2022 $ 23,594,542 $ 428,088 $ 1,029,048 $</t>
+          <t>Gain from debt extinguishment</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
-      <c r="E108" s="5" t="n">
-        <v>-0.360933</v>
-      </c>
-      <c r="F108" s="5" t="n">
-        <v>-25.412611</v>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -6118,22 +5964,20 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Notes          Share capital                surplus               reserve                   Deficit                 equity</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Shares issued in private placement, net of share issuance costs 8(a) 99,840 - 24,960</t>
+          <t>Gain from debt write-off</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" s="5" t="n">
-        <v>0.1248</v>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.006968</v>
+      </c>
+      <c r="F109" s="5" t="n">
+        <v>0.016252</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -6149,17 +5993,21 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Notes          Share capital                surplus               reserve                   Deficit                 equity</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Share based payments 9(a) - - 287,089</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
+          <t>Other expenses</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E110" s="5" t="n">
-        <v>0.287089</v>
+        <v>-0.02</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -6180,22 +6028,24 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Notes          Share capital                surplus               reserve                   Deficit                 equity</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Warrants modified 8(b) - - 9,250</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
+          <t>Net loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E111" s="5" t="n">
-        <v>0.00925</v>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.621001</v>
+      </c>
+      <c r="F111" s="5" t="n">
+        <v>-1.741268</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -6211,22 +6061,24 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Notes          Share capital                surplus               reserve                   Deficit                 equity</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Warrants issued on loan payable 8(b(i)) - - 6,900</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
+          <t>Basic and diluted loss per common share $</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E112" s="5" t="n">
-        <v>0.0069</v>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1e-08</v>
+      </c>
+      <c r="F112" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -6242,22 +6094,20 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Notes          Share capital                surplus               reserve                   Deficit                 equity</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Transfer of share based payments expired 9(a(iv)) - - (523,950)</t>
+          <t>Weighted average number of common shares outstanding – basic and diluted</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E113" s="5" t="n">
+        <v>194.866032</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>0.52395</v>
+        <v>201.250233</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -6278,19 +6128,15 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss - - -</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Balance as at December 31, 2022 $ 23,594,542 $ 428,088 $ 1,029,048 $</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
       <c r="E114" s="5" t="n">
-        <v>-1.621001</v>
+        <v>-0.360933</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>-1.621001</v>
+        <v>-25.412611</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -6311,15 +6157,17 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Balance as at December 31, 2023 $ 23,694,382 $ 428,088 $ 833,297 $</t>
+          <t>Shares issued in private placement, net of share issuance costs 8(a) 99,840 - 24,960</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" s="5" t="n">
-        <v>-1.553895</v>
-      </c>
-      <c r="F115" s="5" t="n">
-        <v>-26.509662</v>
+        <v>0.1248</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -6340,12 +6188,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Shares issued in private placement 8(a) 347,983 - 95,028</t>
+          <t>Share based payments 9(a) - - 287,089</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" s="5" t="n">
-        <v>0.443011</v>
+        <v>0.287089</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -6371,12 +6219,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Shares issued to acquire intangible assets 8(a) 15,000 - -</t>
+          <t>Warrants modified 8(b) - - 9,250</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" s="5" t="n">
-        <v>0.015</v>
+        <v>0.00925</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -6402,12 +6250,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Shares issued to settle loans and borrowings 8(a) 24,000 - -</t>
+          <t>Warrants issued on loan payable 8(b(i)) - - 6,900</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" s="5" t="n">
-        <v>0.024</v>
+        <v>0.0069</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -6433,17 +6281,17 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Share based payments 8(a) - - 63,911</t>
+          <t>Transfer of share based payments expired 9(a(iv)) - - (523,950)</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
-      <c r="E119" s="5" t="n">
-        <v>0.063911</v>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="n">
+        <v>0.52395</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -6464,17 +6312,19 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Warrant modification 8(b) - - 571,026</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr"/>
+          <t>Net loss and comprehensive loss - - -</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E120" s="5" t="n">
-        <v>0.571026</v>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.621001</v>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>-1.621001</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -6495,17 +6345,15 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Warrants issued on loan payable 8(b(i)) - - 6,240</t>
+          <t>Balance as at December 31, 2023 $ 23,694,382 $ 428,088 $ 833,297 $</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" s="5" t="n">
-        <v>0.00624</v>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.553895</v>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>-26.509662</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -6526,14 +6374,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Transfer of share warrants expired 8(b) - 17,274 (17,274)</t>
+          <t>Shares issued in private placement 8(a) 347,983 - 95,028</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E122" s="5" t="n">
+        <v>0.443011</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -6559,17 +6405,17 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Transfer of share-based payments expired 9(a(iv)) - - (158,650)</t>
+          <t>Shares issued to acquire intangible assets 8(a) 15,000 - -</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F123" s="5" t="n">
-        <v>0.15865</v>
+      <c r="E123" s="5" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -6590,19 +6436,17 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Net loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Shares issued to settle loans and borrowings 8(a) 24,000 - -</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
       <c r="E124" s="5" t="n">
-        <v>-1.723325</v>
-      </c>
-      <c r="F124" s="5" t="n">
-        <v>-1.723325</v>
+        <v>0.024</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -6623,17 +6467,207 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Balance as of December 31, 2024 $ 24,081,365 $ 445,362 $ 1,393,578 $</t>
+          <t>Share based payments 8(a) - - 63,911</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" s="5" t="n">
+        <v>0.063911</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Notes          Share capital                surplus               reserve                   Deficit                 equity</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Warrant modification 8(b) - - 571,026</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" s="5" t="n">
+        <v>0.571026</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Notes          Share capital                surplus               reserve                   Deficit                 equity</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Warrants issued on loan payable 8(b(i)) - - 6,240</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" s="5" t="n">
+        <v>0.00624</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Notes          Share capital                surplus               reserve                   Deficit                 equity</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Transfer of share warrants expired 8(b) - 17,274 (17,274)</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Notes          Share capital                surplus               reserve                   Deficit                 equity</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Transfer of share-based payments expired 9(a(iv)) - - (158,650)</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F129" s="5" t="n">
+        <v>0.15865</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Notes          Share capital                surplus               reserve                   Deficit                 equity</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Net loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="n">
+        <v>-1.723325</v>
+      </c>
+      <c r="F130" s="5" t="n">
+        <v>-1.723325</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Notes          Share capital                surplus               reserve                   Deficit                 equity</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Balance as of December 31, 2024 $ 24,081,365 $ 445,362 $ 1,393,578 $</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" s="5" t="n">
         <v>-2.154032</v>
       </c>
-      <c r="F125" s="5" t="n">
+      <c r="F131" s="5" t="n">
         <v>-28.074337</v>
       </c>
-      <c r="G125" t="inlineStr">
+      <c r="G131" t="inlineStr">
         <is>
           <t>-</t>
         </is>
